--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/shawahed_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73893BBA-3515-F948-AF52-9CA600E314CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560547BF-7169-6048-A93E-C75D228B92A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9780" yWindow="640" windowWidth="19620" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="268">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -506,9 +506,6 @@
   </si>
   <si>
     <t>عبد العزيز بن مراد بن شمسي العمري</t>
-  </si>
-  <si>
-    <t>1160946354</t>
   </si>
   <si>
     <t>علي بن بشير بن احمد بن محمد خواجي</t>
@@ -1581,7 +1578,7 @@
         <v>57</v>
       </c>
       <c r="D27" s="1">
-        <v>72</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
@@ -1595,7 +1592,7 @@
         <v>57</v>
       </c>
       <c r="D28" s="1">
-        <v>51</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
@@ -1609,7 +1606,7 @@
         <v>57</v>
       </c>
       <c r="D29" s="1">
-        <v>73</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
@@ -1623,7 +1620,7 @@
         <v>57</v>
       </c>
       <c r="D30" s="1">
-        <v>52</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
@@ -1637,7 +1634,7 @@
         <v>57</v>
       </c>
       <c r="D31" s="1">
-        <v>53</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
@@ -1651,7 +1648,7 @@
         <v>57</v>
       </c>
       <c r="D32" s="1">
-        <v>54</v>
+        <v>203</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
@@ -1665,7 +1662,7 @@
         <v>57</v>
       </c>
       <c r="D33" s="1">
-        <v>55</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
@@ -1679,7 +1676,7 @@
         <v>57</v>
       </c>
       <c r="D34" s="1">
-        <v>74</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1693,7 +1690,7 @@
         <v>57</v>
       </c>
       <c r="D35" s="1">
-        <v>56</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1707,7 +1704,7 @@
         <v>57</v>
       </c>
       <c r="D36" s="1">
-        <v>75</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1721,7 +1718,7 @@
         <v>57</v>
       </c>
       <c r="D37" s="1">
-        <v>76</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
@@ -1735,7 +1732,7 @@
         <v>57</v>
       </c>
       <c r="D38" s="1">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
@@ -1749,7 +1746,7 @@
         <v>57</v>
       </c>
       <c r="D39" s="1">
-        <v>57</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1763,7 +1760,7 @@
         <v>57</v>
       </c>
       <c r="D40" s="1">
-        <v>78</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1777,7 +1774,7 @@
         <v>57</v>
       </c>
       <c r="D41" s="1">
-        <v>58</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -1791,7 +1788,7 @@
         <v>57</v>
       </c>
       <c r="D42" s="1">
-        <v>59</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -1805,7 +1802,7 @@
         <v>57</v>
       </c>
       <c r="D43" s="1">
-        <v>79</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -1819,7 +1816,7 @@
         <v>57</v>
       </c>
       <c r="D44" s="1">
-        <v>80</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1833,7 +1830,7 @@
         <v>57</v>
       </c>
       <c r="D45" s="1">
-        <v>60</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1847,7 +1844,7 @@
         <v>57</v>
       </c>
       <c r="D46" s="1">
-        <v>81</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1861,7 +1858,7 @@
         <v>57</v>
       </c>
       <c r="D47" s="1">
-        <v>61</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1875,7 +1872,7 @@
         <v>57</v>
       </c>
       <c r="D48" s="1">
-        <v>62</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
@@ -1889,7 +1886,7 @@
         <v>57</v>
       </c>
       <c r="D49" s="1">
-        <v>82</v>
+        <v>231</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
@@ -1903,7 +1900,7 @@
         <v>57</v>
       </c>
       <c r="D50" s="1">
-        <v>83</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -1917,7 +1914,7 @@
         <v>57</v>
       </c>
       <c r="D51" s="1">
-        <v>84</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -1931,7 +1928,7 @@
         <v>57</v>
       </c>
       <c r="D52" s="1">
-        <v>63</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
@@ -1945,7 +1942,7 @@
         <v>57</v>
       </c>
       <c r="D53" s="1">
-        <v>65</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
@@ -1959,7 +1956,7 @@
         <v>57</v>
       </c>
       <c r="D54" s="1">
-        <v>85</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
@@ -1973,7 +1970,7 @@
         <v>57</v>
       </c>
       <c r="D55" s="1">
-        <v>66</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
@@ -2001,7 +1998,7 @@
         <v>114</v>
       </c>
       <c r="D57" s="1">
-        <v>90</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
@@ -2015,7 +2012,7 @@
         <v>114</v>
       </c>
       <c r="D58" s="1">
-        <v>91</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
@@ -2043,7 +2040,7 @@
         <v>114</v>
       </c>
       <c r="D60" s="1">
-        <v>92</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
@@ -2141,7 +2138,7 @@
         <v>114</v>
       </c>
       <c r="D67" s="1">
-        <v>94</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
@@ -2155,7 +2152,7 @@
         <v>114</v>
       </c>
       <c r="D68" s="1">
-        <v>95</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
@@ -2183,7 +2180,7 @@
         <v>114</v>
       </c>
       <c r="D70" s="1">
-        <v>96</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
@@ -2239,7 +2236,7 @@
         <v>114</v>
       </c>
       <c r="D74" s="1">
-        <v>97</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
@@ -2295,7 +2292,7 @@
         <v>114</v>
       </c>
       <c r="D78" s="1">
-        <v>98</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
@@ -2316,8 +2313,8 @@
       <c r="A80" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>162</v>
+      <c r="B80" s="1">
+        <v>1160946354</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>114</v>
@@ -2328,167 +2325,167 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D81" s="1">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="C82" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D82" s="1">
-        <v>116</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C83" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D83" s="1">
-        <v>117</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C84" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D84" s="1">
-        <v>118</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C85" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D85" s="1">
-        <v>120</v>
+        <v>98</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C86" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D86" s="1">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C87" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D87" s="1">
-        <v>122</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C88" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D88" s="1">
-        <v>123</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C89" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D89" s="1">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C90" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D90" s="1">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C91" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D91" s="1">
-        <v>129</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C92" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D92" s="1">
         <v>131</v>
@@ -2496,13 +2493,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="C93" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D93" s="1">
         <v>130</v>
@@ -2510,13 +2507,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="C94" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D94" s="1">
         <v>132</v>
@@ -2524,13 +2521,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="C95" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D95" s="1">
         <v>133</v>
@@ -2538,13 +2535,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C96" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D96" s="1">
         <v>134</v>
@@ -2552,13 +2549,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="C97" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D97" s="1">
         <v>135</v>
@@ -2566,13 +2563,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="C98" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D98" s="1">
         <v>136</v>
@@ -2580,13 +2577,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="C99" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D99" s="1">
         <v>137</v>
@@ -2594,13 +2591,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="C100" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D100" s="1">
         <v>138</v>
@@ -2608,13 +2605,13 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="C101" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D101" s="1">
         <v>139</v>
@@ -2622,13 +2619,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="C102" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D102" s="1">
         <v>140</v>
@@ -2636,13 +2633,13 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C103" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D103" s="1">
         <v>141</v>
@@ -2650,13 +2647,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C104" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D104" s="1">
         <v>142</v>
@@ -2664,13 +2661,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="C105" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D105" s="1">
         <v>144</v>
@@ -2678,13 +2675,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="C106" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D106" s="1">
         <v>145</v>
@@ -2692,13 +2689,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C107" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D107" s="1">
         <v>146</v>
@@ -2706,7 +2703,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B108" s="1">
         <v>1171904780</v>
@@ -2715,12 +2712,12 @@
         <v>57</v>
       </c>
       <c r="D108" s="1">
-        <v>67</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B109" s="1">
         <v>1170366247</v>
@@ -2729,12 +2726,12 @@
         <v>57</v>
       </c>
       <c r="D109" s="1">
-        <v>68</v>
+        <v>217</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B110" s="1">
         <v>1167502283</v>
@@ -2743,12 +2740,12 @@
         <v>57</v>
       </c>
       <c r="D110" s="1">
-        <v>87</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B111" s="1">
         <v>1172242503</v>
@@ -2757,12 +2754,12 @@
         <v>57</v>
       </c>
       <c r="D111" s="1">
-        <v>69</v>
+        <v>218</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B112" s="1">
         <v>1173217702</v>
@@ -2771,12 +2768,12 @@
         <v>57</v>
       </c>
       <c r="D112" s="1">
-        <v>88</v>
+        <v>237</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B113" s="1">
         <v>1168684411</v>
@@ -2785,12 +2782,12 @@
         <v>57</v>
       </c>
       <c r="D113" s="1">
-        <v>70</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B114" s="1">
         <v>1172306696</v>
@@ -2799,12 +2796,12 @@
         <v>57</v>
       </c>
       <c r="D114" s="1">
-        <v>71</v>
+        <v>220</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B115" s="1">
         <v>8885500012</v>
@@ -2813,26 +2810,26 @@
         <v>57</v>
       </c>
       <c r="D115" s="1">
-        <v>86</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D116" s="1">
-        <v>89</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B117" s="1">
         <v>1163250507</v>
@@ -2841,40 +2838,40 @@
         <v>114</v>
       </c>
       <c r="D117" s="1">
-        <v>93</v>
+        <v>46</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D118" s="1">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D119" s="1">
-        <v>101</v>
+        <v>54</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B120" s="1">
         <v>1165324110</v>
@@ -2883,12 +2880,12 @@
         <v>114</v>
       </c>
       <c r="D120" s="1">
-        <v>102</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B121" s="1">
         <v>4148138052</v>
@@ -2902,7 +2899,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B122" s="1">
         <v>1164420844</v>
@@ -2911,12 +2908,12 @@
         <v>114</v>
       </c>
       <c r="D122" s="1">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B123" s="1">
         <v>4615745579</v>
@@ -2925,12 +2922,12 @@
         <v>114</v>
       </c>
       <c r="D123" s="1">
-        <v>104</v>
+        <v>57</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B124" s="1">
         <v>1181813641</v>
@@ -2939,12 +2936,12 @@
         <v>114</v>
       </c>
       <c r="D124" s="1">
-        <v>105</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B125" s="1">
         <v>1163831744</v>
@@ -2953,12 +2950,12 @@
         <v>114</v>
       </c>
       <c r="D125" s="1">
-        <v>106</v>
+        <v>59</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B126" s="1">
         <v>4147413001</v>
@@ -2972,7 +2969,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B127" s="1">
         <v>1163490434</v>
@@ -2981,15 +2978,15 @@
         <v>114</v>
       </c>
       <c r="D127" s="1">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>114</v>
@@ -3000,21 +2997,21 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D129" s="1">
-        <v>110</v>
+        <v>88</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B130" s="1">
         <v>1157574326</v>
@@ -3028,7 +3025,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B131" s="1">
         <v>4158162166</v>
@@ -3037,12 +3034,12 @@
         <v>114</v>
       </c>
       <c r="D131" s="1">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B132" s="1">
         <v>2423235403</v>
@@ -3051,12 +3048,12 @@
         <v>114</v>
       </c>
       <c r="D132" s="1">
-        <v>114</v>
+        <v>64</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B133" s="1">
         <v>4161468287</v>
@@ -3065,12 +3062,12 @@
         <v>114</v>
       </c>
       <c r="D133" s="1">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B134" s="1">
         <v>1164394189</v>
@@ -3079,12 +3076,12 @@
         <v>114</v>
       </c>
       <c r="D134" s="1">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B135" s="1">
         <v>1164072280</v>
@@ -3098,7 +3095,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B136" s="1">
         <v>4146865078</v>
@@ -3112,7 +3109,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B137" s="1">
         <v>1167047925</v>
@@ -3121,12 +3118,12 @@
         <v>114</v>
       </c>
       <c r="D137" s="1">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B138" s="1">
         <v>2358054076</v>
@@ -3140,7 +3137,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B139" s="1">
         <v>1167005832</v>
@@ -3154,21 +3151,21 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D140" s="1">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B141" s="1">
         <v>4148138326</v>
@@ -3182,83 +3179,83 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C142" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D142" s="1">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C143" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D143" s="1">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B144" s="1">
         <v>39357241</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D144" s="1">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C145" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D145" s="1">
-        <v>127</v>
+        <v>105</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B146" s="1">
         <v>1164514281</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D146" s="1">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B147" s="1">
         <v>1161684004</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D147" s="1">
         <v>148</v>
@@ -3266,13 +3263,13 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B148" s="1">
         <v>1161411887</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D148" s="1">
         <v>149</v>
@@ -3280,13 +3277,13 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B149" s="1">
         <v>170498263</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D149" s="1">
         <v>173</v>

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/shawahed_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560547BF-7169-6048-A93E-C75D228B92A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1484B5C-8DA5-BE4C-923A-86193783B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9780" yWindow="640" windowWidth="19620" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1788,7 +1788,7 @@
         <v>57</v>
       </c>
       <c r="D42" s="1">
-        <v>208</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/shawahed_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1484B5C-8DA5-BE4C-923A-86193783B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ECF687-A9CB-4940-B0F6-EB575EA54633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9780" yWindow="640" windowWidth="19620" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1788,7 +1788,7 @@
         <v>57</v>
       </c>
       <c r="D42" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aburakanalhazmi/shawahed_local/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/87c4edf3438519d4/عام 1-1448/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ECF687-A9CB-4940-B0F6-EB575EA54633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F6E8CE74-9F90-1D44-8069-E59F86DF4ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B175C379-3F5C-AF48-B8ED-9EBEACBA8997}"/>
   <bookViews>
-    <workbookView xWindow="9780" yWindow="640" windowWidth="19620" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="296">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -824,13 +837,97 @@
   </si>
   <si>
     <t>نايف محمد أحمد هندوان</t>
+  </si>
+  <si>
+    <t>محمد نايف علي ال حسين</t>
+  </si>
+  <si>
+    <t>رابط شواهد</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=ed55cb20a1b99a413067b807cd447b355cd0b705cc09b29c0f7a0c8dcc8bb592</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=5a4d17445bdb98c8662dee2efe13d45e1d99843d18d85500148197fd0bd76dcd</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=f2ba09ea331454fd5a2e3b827765de37ece974fb00b2a23bcdf2627233f372a1</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=4dfb3dddda04b678fec8a5665a7311084eeccc951f40d8fd2109dea624ebe9aa</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=dcd4e3e9c149d8bf434e0dab4faf0014e98cf5ada89af14309b364c8636eb5f8</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=56f40d4089d0134701a06f7400010efc0520ed5bba5d5ed373097547ccbe243d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=fa9ea50a32491c634cf8217186e26edc4bf9c4f8a92686c5e317cfd5e7ba29bf</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=c5f4200efa8852b77c9b0f61e026458d4db2cdb8a52db48dae27c35c8935fdcc</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1c7b8636e92a3fc54538cb31fdd6bcb9416ac83a0faa31aeea5e698b3ec78097</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=85db6adec1e2a7242f6cd023e3747d26ce80a467885637677758a4f9ac5cd01d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2e75fda9c2b856fa392dc0e8aee1fb5551a93a05caada3073578911ff20d68f7</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=979e2a59f45cff5eaeeff9a2b57181d2199f79c3b80244d0816abeb555a0a2d5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=bf763bfcfe2cd9a221d43faa08d8326d4490f9e6570965ce5dfeca63c1e618fc</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=5c0d5904f6b27fa334cda4f6587834edb996cdff485549f19867718bd4e48112</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=15680fbdd2fef75ae48029f1e06029f2cc9083e2025b0ce605f2d9e16131f9f6</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0da998757455621d230029fdc39e8d90ff60ddc94c03cf9e7d1b64cbf8b948f9</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=792e889d03c8b7bef85b95586d4fe7382a9663c59ce1043e075d9a622991e50d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=69122a37b61fe48a40b6ba0b70b3521d953663f907ce6b294d3b3cd61a488bda</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=7d47571d08bd8d34955f83c4eddfe53504834e4c1d39f401525284ed95758ec2</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=8339b68285e79cdf537dc3c52bb0d7acd158cff1484f5b0c84bc810cb95d396d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=331ff39dd71302e1e238c373d15ad69438880cd8e289d69f6edfddbf62ee6445</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=67532ca1bd1d47488c8c0fdb80e1c5095c6795583da26952fdc2aca8e5db4789</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=6c145c12258a9113cbdb19a552e8c71022c7500fa4c8172d9716143044f7ddc2</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=cef729f404f2271396bceb2f20cf3d19f9dcd40d0b266f8b0444ea7197975e2c</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=d48f2db453443590474e09cabdf652cabda7f2e97845eef5e529e1af570f8304</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1a5ded01a038a542fbf7a134f8484bf64c1b93c108e849ea9d89e84b65770f9f</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,6 +958,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -879,11 +1008,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -891,10 +1022,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink" xfId="3" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Normal" xfId="1" xr:uid="{547660EB-2ECC-7847-AA09-94C772084EC8}"/>
+    <cellStyle name="ارتباط تشعبي" xfId="2" builtinId="8"/>
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal" xfId="1" xr:uid="{547660EB-2ECC-7847-AA09-94C772084EC8}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1194,16 +1338,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D149"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:E150"/>
+  <sheetFormatPr defaultColWidth="8.82421875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="45" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="44.9921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.2734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.29296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.82421875" style="1"/>
+    <col min="5" max="5" width="44.37890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1216,8 +1361,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E1" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1230,8 +1378,11 @@
       <c r="D2" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E2" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1244,8 +1395,11 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E3" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -1258,8 +1412,11 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E4" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1272,8 +1429,11 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E5" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1286,8 +1446,11 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E6" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -1300,8 +1463,11 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E7" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -1314,8 +1480,11 @@
       <c r="D8" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E8" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -1328,8 +1497,11 @@
       <c r="D9" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E9" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1342,8 +1514,11 @@
       <c r="D10" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E10" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -1356,8 +1531,11 @@
       <c r="D11" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E11" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1370,8 +1548,11 @@
       <c r="D12" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E12" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -1384,8 +1565,11 @@
       <c r="D13" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E13" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
@@ -1398,8 +1582,11 @@
       <c r="D14" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E14" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -1412,8 +1599,11 @@
       <c r="D15" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E15" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -1426,8 +1616,11 @@
       <c r="D16" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E16" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
@@ -1440,8 +1633,11 @@
       <c r="D17" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E17" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>37</v>
       </c>
@@ -1454,8 +1650,11 @@
       <c r="D18" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E18" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -1468,8 +1667,11 @@
       <c r="D19" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E19" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>41</v>
       </c>
@@ -1482,8 +1684,11 @@
       <c r="D20" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E20" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>43</v>
       </c>
@@ -1496,8 +1701,11 @@
       <c r="D21" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E21" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
@@ -1510,8 +1718,11 @@
       <c r="D22" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E22" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>47</v>
       </c>
@@ -1524,8 +1735,11 @@
       <c r="D23" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E23" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>49</v>
       </c>
@@ -1538,8 +1752,11 @@
       <c r="D24" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E24" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>51</v>
       </c>
@@ -1552,8 +1769,11 @@
       <c r="D25" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E25" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
@@ -1566,8 +1786,11 @@
       <c r="D26" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E26" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>55</v>
       </c>
@@ -1581,7 +1804,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>58</v>
       </c>
@@ -1595,7 +1818,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>60</v>
       </c>
@@ -1609,7 +1832,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -1623,7 +1846,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>64</v>
       </c>
@@ -1637,7 +1860,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -3219,7 +3442,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
         <v>262</v>
       </c>
@@ -3233,7 +3456,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
         <v>264</v>
       </c>
@@ -3247,7 +3470,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
         <v>265</v>
       </c>
@@ -3261,7 +3484,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
         <v>266</v>
       </c>
@@ -3275,7 +3498,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
         <v>267</v>
       </c>
@@ -3289,7 +3512,52 @@
         <v>173</v>
       </c>
     </row>
+    <row r="150" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A150" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B150" s="4">
+        <v>4160034346</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" s="1">
+        <v>27</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{492A84B9-29D4-E840-98D8-E255D7A381BF}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{19D4A8AC-095E-8840-A219-646691D9C207}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{69671F9D-FAEC-0046-B67C-504591BA2EA0}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{CEB8D81D-1C74-0B4D-9EBF-6BAFBEDF0128}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{5CE1B731-B841-EF49-8A0D-E66BEFAAD5B4}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{C6A7D1C2-A36D-B145-AAFA-EE40B70309C5}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{F7CCEF89-C8B3-6648-A703-C9EC69CFE189}"/>
+    <hyperlink ref="E9" r:id="rId8" xr:uid="{A3EDD4E2-51CE-FB40-B60A-A2ECEA3DB9C3}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{80D1686F-C8F0-684E-9B70-2F8F99399DD3}"/>
+    <hyperlink ref="E11" r:id="rId10" xr:uid="{9FE0C707-E2FE-6C47-ABE9-F34C02954F57}"/>
+    <hyperlink ref="E12" r:id="rId11" xr:uid="{C4103472-6C9D-CC4E-8AA0-B46535DE87B8}"/>
+    <hyperlink ref="E13" r:id="rId12" xr:uid="{F13BC91D-9674-AD46-AC43-C84D3D6689BA}"/>
+    <hyperlink ref="E14" r:id="rId13" xr:uid="{3A822F64-47F4-A045-B287-930717B5CB4A}"/>
+    <hyperlink ref="E15" r:id="rId14" xr:uid="{B43ABDA9-FE0E-1543-88B6-8E3AD63C339D}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{48E23965-A708-2D4B-84B2-8CF24A58E39D}"/>
+    <hyperlink ref="E17" r:id="rId16" xr:uid="{3AF34922-FED3-5546-9B56-12CBFBCF7EA9}"/>
+    <hyperlink ref="E18" r:id="rId17" xr:uid="{C70870F2-B1E9-EF46-8C2E-E42392732E62}"/>
+    <hyperlink ref="E19" r:id="rId18" xr:uid="{D69E7174-9D27-534F-A0DB-25E1E7DD2931}"/>
+    <hyperlink ref="E20" r:id="rId19" xr:uid="{295A748B-F07E-8B4C-A884-76ABBA430E0E}"/>
+    <hyperlink ref="E21" r:id="rId20" xr:uid="{AF83CAC5-A602-4B4F-9B94-5D8DB04F4963}"/>
+    <hyperlink ref="E22" r:id="rId21" xr:uid="{27790322-4ADB-D541-9639-77E091B3139E}"/>
+    <hyperlink ref="E23" r:id="rId22" xr:uid="{6E782B56-EB08-0147-986B-E1CA3DFC2173}"/>
+    <hyperlink ref="E24" r:id="rId23" xr:uid="{9B815F51-A29E-5442-A42F-F973784660A4}"/>
+    <hyperlink ref="E25" r:id="rId24" xr:uid="{95F586DA-97A7-1B4E-8CC6-C0D33B0FB054}"/>
+    <hyperlink ref="E26" r:id="rId25" xr:uid="{08C8D0D0-F61E-2641-A4C3-D928A3793B65}"/>
+    <hyperlink ref="E150" r:id="rId26" xr:uid="{804CCF4C-5A7B-9B48-98CA-E205F3A96300}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/87c4edf3438519d4/عام 1-1448/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F6E8CE74-9F90-1D44-8069-E59F86DF4ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B175C379-3F5C-AF48-B8ED-9EBEACBA8997}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{F6E8CE74-9F90-1D44-8069-E59F86DF4ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18CD909D-85FF-1645-A1D9-76996F0374BA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="419">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -921,6 +921,375 @@
   </si>
   <si>
     <t>https://shawahid-saleh.web.app/student.html?t=1a5ded01a038a542fbf7a134f8484bf64c1b93c108e849ea9d89e84b65770f9f</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=282584f8fa7dd780fd048ae3ce98c2b53307aa015182a7ea68348342afbad4d0</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=40c9d77845979d132da43e7340d04e6e2c9a86675c9c84ef961b4381fdde02c5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=a67aaae18d2211debadf925cd72263840b9328d75813c620316cf4e677032c92</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=79df67b69520f0da5bd589c7be7c845c3f9f283bf69ef9c089e69138c3e7f9e2</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=fdefcc01d6ec19eeacecb108c481e52cce73d064ee7f6577b417d71168c73232</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2706fe6592892439cfed69043afe228557aacd546adc7161669dbcc73dea0ea0</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9bbac9848dad5509a30b1034c8a9388a2847c0ae0ffad1eb1dffb9c55aca4b50</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9f9653538630cd23e17bbcd22e667f78342247b09d859a573cd3a103b69c788e</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=46e1eb045bfdfc9c0ca8a3c19bef9c1744bde372e78e2f7ad487256de4fceec8</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=bea956c4868a209e01d7dbedf8fe402edc8177f017886a3a79305944c644d283</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=3aa0148e853ef2f4538ad41a39c23782c9d838b3c5981a2536085ba0e10144e9</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=b72c4cfa445f09c83531e1a60c73fa1472d6794b671d7e4fe078e2717b4606e3</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=c8eddfb190a23c74900b396ca79d424481752a29230e4c790d9ba898f2a8effb</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=fe8e03bd8a052a0f3e5664ba7a026ddc2a697d8406a2ce4914a11a439f1edbfe</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=20c75708a94f7a8bf52bae09259f116b86db02e5e318201a91d980082a101584</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=83999f4911c7910f7a9dd6ecfc0dffd36c88ff55b2c4e1dd16b0928189e4f439</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=ba9daba14d271c1d831f7bd5827e576034d4a2736a878689ef9f7af5d0d3daae</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=34c54a47e975ff1d318753cf6342461af473505931fad3b59c059c3342a2bfa7</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=be61081167c08a6da547e690a29b3a8709dbe803db51747eb3c793d599c4acf3</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=f2a8f64dca09d076ea9ac9022de9281dd5a8761289b8886038e7dae72d095f6e</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=5e08178f886c4d625d3dd66da34dcab813948e71c6d30ca471683f5073c4262f</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1ae374bae6c7ce46e14380d453f378affa36fc8b7615634a1ce43cd46f6824b5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=c16cb731383b5b1d374f9709840852c9c4785e28d94bd20064a4c87c593f796d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2d3edfb62fa90758f54b13d3d8255285e53ceacb490b0df61fbbd7babf420d40</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=5c4b4fa5d6864a996bf2f235d8d378e76d209b4ddaa4024db650a59be0459d1a</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=f9f49d809786e4b96c9564e4a0af005448a56f94e4f8940e2656112be9a328e5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9f0d9b9ab6b2ee057763d50bcbd29bd5982c5a310cbca0b0ddd9ec93f738266b</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=bcc6469415b4e083e13ba4cdcd136624b725423555ef04efccfd0dec37371d8a</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2df7eed309bebb46124a48bea720dc7b781a31d955bfc1f3206de51f7e143386</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0dd521efe236e54feaa37daee6c8e42d850b8b9442afc3e096843c1ada34bfdb</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9c81b696197b1e57803fdc9ac27ddb3318947bf979e787f7370d1a7fcd1c098f</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=18d544c31c7617d850d415fc4df343240cf1306eb1ea43134684978fcbb05cbc</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9f004c8f27a8f259825fa7bc2df00669d495dcb6a5c1393e4b381e9377f06359</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=66af8c003fc1fd16f50fec303f576643a17cb7b057bcf81c215132c71f3c5f66</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=6a8405a2137bec7e317291201d917057c9445a85f9a041934d0a8f22e5ceae9b</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=e9bcd9564c790a60c8b317841002c7c934d3e26185af2d62b8af7dd3e147761c</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=de47fd6130053733a5cc5d3ed5f487cd8d91af745a0a66f746f5765c3b097fd9</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0b4c4787604dba59a4f498c20c08626f47f76e8c525a860341a01a23536da460</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=a3b740c2343d5d93af7b6252e798942899575eb232fa99599240a2724ff5e470</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=67da11a6a5fa1170e6eea79f99211b94d8656471dbe61a54ad4e9acd549ad04b</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=266966af8e1dd3e2be9a28d64be2d1c5345f75146a8d70ba740cb7683db810bb</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=e62d885439f2b3cb3653f768f55944a652fd326c34137e4c4f9df99acdbc3747</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=242c967406e1ab861fc282d41d3c4849062ffa70b8d4d79d749d77da72c94b7f</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=eb82f15bbb4cdb04c386a3b59bf2c1dd7cae6a544896f23f07b4c72b58893d34</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=37eeeff125420a4fb2c3e249b57e7867bab82aacafe3be1b8386e0079a71695d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=f075796dbdec6d72fb2b04c44d66bb8a25cb0eaa7914dd1a7349f3ac4d06fa3c</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=67732c89439580a50697aba305026f12113adfe3ee3dcb8344be2f754d3fedd1</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0b9c577529b12c2b3ae5c26d67265fa695feeb017002ebfa4535b4c5d3496011</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=e4bfe66c73d7ce1998ec146579e430d8a107041a6af360c0e581394896897d15</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=6ef9258a6a8e6aa717b2b410ec219aaf7d6175558347363091dbf2005b182f7a</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=6f993b35fd218bfcac45cd5eb9df2b51265281f01b7ccf0ae29bf3f2235c4a9b</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=a5dbc8d3ec508f483fc1e6bff2b0a62e0db24032e801c4f1177b5bb982f928eb</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=24a14bff6fd1c255943cbab0ca3e5dbd863483458ceacb7306b9e8aab55f7c6d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=86280e30f249be21c8b6f32c015854be17c2a08c7c25f1e34c6ad8fa16fe6c03</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=c23b6541d35ef1549e38e70c3b15f8e9a0558bd0a47540e12d6260e15bacaaa6</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=bec134b5e63154e99d9be78bad299d3e14727e01858d942a39f56514d42c5076</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1d2bcf4c329d591a99a6016c933f543c06fb54cd15a438c480b62bc62cb641a2</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1811416f0d4574c82e3d6c622e47f7c9fa84fb1a5a163c3df45bbc25a50824e0</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9b6c3aaf0410ad463d0c97985254da47e1a56f509256f102b2cf72d653edc614</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=f41cc0c0e94d64bd08340bd408cf3b2968c7a8e8ad54a2528c5534984b62e0d5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=3fe7c5d35aa080c7ec1840a934010202331d1528927a628132f052e4fcb4c200</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1cfb4aefbc957b47c5e0adccdf6191e045254f3085179615bfb3eccc66ed25ec</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=8ce43c70ad884c66908fa0c5b53da98e6a1c42eef54e114a72d0d9fb739972e4</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=bf549978bd8fd7d26ad68473380505b9cc4d640e5435b88d77146633aa7758f3</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=b9b4ac8eb92c756760bbd32713baa837fc71079aaac5f46a86d152abf5dc7845</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=d5731016e9c789273d27eac2f2e72df2c2b7669601e26b1431372a66f3fb411e</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=638fc3b8c17b59399036473c4c14c2ec0938eb29dd7106c8ca6d673ec6ab3ee6</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=029babf41ab2d0f2fa9de71ce184b844f1039d6d5a6cb1c062049fa41c9f48ef</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=8f57c7c9f925239194e0dc8de0a1373259ca69dff678478fa75cf7eb9fb4bb05</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=05dcd04f72d651e8a088abaeef712cab48f7f9bfabbb0bf91da673f08d99925d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=aa20bd953e98d42c75f4bcef8b6467d72dcd02d5d7d24c821e03df868932a98d</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=a868f5310d7ed3585b3410f9f07c6d94ca74f71375ce95481df08ff11e96f2f9</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2034b621e1530a372cd6e8cee45f28699e199e054ecc6dd39c68077eb71a5655</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9c2c3e198d98332cf80f260f914b3d7202e1a000f017b68d0b54b29ec236455a</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=7c980fd437f02555fb227dfab653bec5312e1eaa4b9a8d1ce9d16314660ab221</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=7b2f7a686406bd37951f2a1151b38f6502f8dea06dc92fca36c1a561ea4a9279</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=6548e522954332a7f50c10edd36f4902c96848465b29e6226060097d4a2f3aa2</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=ef39f6e52aa6e83b31403aee9b33c9722fb054993cc6b13baea695cbb4a87940</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=da80ec5ae91d5c44914a0069ddd6683c78c1fdb126b3c1a3129d7d963565530a</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0fc9cd7fca67dbc25c3558b8452d76f09f8bb4ca41f1153f10fcb9b868b5e598</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2bb2d4eff1706ea71d66e6ab01bf9ac4d4d94169c99521cfac50161f9aa91053</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=abab5fdb2e5c94d8a892a5c24dcf4a7e08ddc4fe62e16ffb9303608e50541ac5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=d98198d18be883ad8f541a094c81e1dc3b849fee0ef5bd267405a4efa45bef7f</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=236079faf35d6bdb319076b42929d986cb727f6a7490a2f4ff549b29e06d9ebc</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=22d5a2cd55dcbb7d41b4df751dfe0d7201666898ee9e5db738a73ef95032b0d6</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=286ec966fdb8ccc1af284855193e089774eeda4d02a3aed096e9d1bd5099c1ba</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=eb6e392d198b47404f50ad0a70b6eb4d0828c88f713f32eb1af534215e8bb643</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=b2abacc30b7e2ae940d0b879c9bb88cbfa1136e31271bf25d7bf458fae678786</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=16f800e57f9c56612d5764e91ee05ac2f0ffdf4631f881e7d1b133338a090b00</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=ad8015916bd1b7ec5fa903ed5dbb94a959bdaab2399a25ff2634a8d0958da5a5</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0a532b67814d3b7179b02d1ba540ddc198df200859a7079854405ef7be2c6fc1</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=0aabb2a95ad0f5d6cb18d9389ae35526cb1b11ea5d6009ecca96f17cf4819798</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=335b8d6259af3771c48668de9f91d85bfddb670d3e55edca144064902bf581a0</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=8ec762194adcd2f9a8ce12dacc4bcba204d0470b7928c9cf499140f4359e72a1</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=d6865e9f84d7f8e189d1b1b1b83969193a707ea44685ccfa3171f397f6b98a89</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=4f3bde093d8659ec7c7935427407b4ef8e460c9b1f9690ff4f3c58ddcf9e97ab</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2408004b837e1571179e55c349b9cbded48005ec83a3eac4e69f41ba1af71795</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=cdf21cea148a17ec49138db9774f881bebf661219694128a92a10b282482671c</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=216ef8221bcec06b8fff13ff6d85f2649f6e34710014c79f22accb3970e61c85</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=046f0536442f12afcb0a4e9611f9b87bcdd4e9727a3c93374ce667b5e01739be</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=c271b256b45a4898e5649e7c6a8141f87b4a600598f64d27e40a785993485d67</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=1b56318ce3ba9d7fe0f5fc8d881bf8af389a23338ecc068a634e8da946018179</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=4f26b13de23e4e1126a207edd1c54d29af30e5201318ed10fbe599f4da6d5a7b</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=840d87560740631f1c452b16dba69712f5e03629f555cfcb65ae8f15f0e547d7</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=9f39009360bbd47ee99596ef16d6a0e44c77803545c86455854afe7d522076ce</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=184e4ee13a9ff712ad07dbd15965df0d5300a59a19b9783e8256942906482c82</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=89f10202e6ff0717ebf3c7735011a816ed21c73e883abe5cf11ac340d113f5e0</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=521c85e5f98789f0547db6b27904e2ea8770f03c6487e07c1c1e238fba817e99</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=7a43926affcc71406a751aea9613c9b9c3ab6e3d5f17fb66c4d0bc5743aa7095</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=2cc0fada82e76af403f1cb33fbda4ec137ddb065eeae9826b4b182bef050245c</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=4a9cfa64b67e11c948b452330e2a58842ee5623e2cfb749a87ef946cd1681c59</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=d7a5ae0a5ad322d849bb13cd7cf976d04c8fa30420dbc51653007df8ea2e7b34</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=ec82ceb7f2f7e455f91f4c9b0bb541f8a7f414d3acdd2eefa668b63e4e5f02dc</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=5a4fbe4313612f75a564647c9c257b3b965538c7108b84865ef3c5efa17d0708</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=400de147c43c5ceaf4cad0e55ec9ead549a0a99f249b19b4a438c0c151e78e70</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=cad5e2c53924a68593457061da81cc43a1fa13121525659c146e52894b54ea35</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=c102ab06366e4d087ae490760f12a2305fc50906ccb5a3d304e938a7e1c5abd9</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=4bba56ca3151adc996ef83cff3b68d5351d7ea7a1ac70250dffb84764a8e02bc</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=4b6992198af650383b9c6e6f31b5c09b141632a42e05ccabcc50a0eaca51ce33</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=e5b0abd37852653cdae46fe524876118ed207829f0c6d806b5c0dba1037a0b37</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=067d219b027d17991e48c554585a735ff7c17606d4337b3382c38cab63f3e388</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=61d459a810109caeedbe07d300cc7d3151ca6dcbb6f1ccb731c7469d5cd44bb9</t>
+  </si>
+  <si>
+    <t>https://shawahid-saleh.web.app/student.html?t=b82cc9017330d4d1bc606e520af660dbbe20db2cb4b2bb4dd337cadd40f39125</t>
   </si>
 </sst>
 </file>
@@ -1803,6 +2172,9 @@
       <c r="D27" s="1">
         <v>221</v>
       </c>
+      <c r="E27" s="7" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
@@ -1817,6 +2189,9 @@
       <c r="D28" s="1">
         <v>200</v>
       </c>
+      <c r="E28" s="7" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
@@ -1831,6 +2206,9 @@
       <c r="D29" s="1">
         <v>222</v>
       </c>
+      <c r="E29" s="7" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
@@ -1845,6 +2223,9 @@
       <c r="D30" s="1">
         <v>201</v>
       </c>
+      <c r="E30" s="7" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
@@ -1859,6 +2240,9 @@
       <c r="D31" s="1">
         <v>202</v>
       </c>
+      <c r="E31" s="7" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
@@ -1873,8 +2257,11 @@
       <c r="D32" s="1">
         <v>203</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E32" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>68</v>
       </c>
@@ -1887,8 +2274,11 @@
       <c r="D33" s="1">
         <v>204</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E33" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>70</v>
       </c>
@@ -1901,8 +2291,11 @@
       <c r="D34" s="1">
         <v>223</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E34" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
@@ -1915,8 +2308,11 @@
       <c r="D35" s="1">
         <v>205</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E35" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>73</v>
       </c>
@@ -1929,8 +2325,11 @@
       <c r="D36" s="1">
         <v>224</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E36" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>74</v>
       </c>
@@ -1943,8 +2342,11 @@
       <c r="D37" s="1">
         <v>225</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E37" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
@@ -1957,8 +2359,11 @@
       <c r="D38" s="1">
         <v>226</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E38" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>78</v>
       </c>
@@ -1971,8 +2376,11 @@
       <c r="D39" s="1">
         <v>206</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E39" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>80</v>
       </c>
@@ -1985,8 +2393,11 @@
       <c r="D40" s="1">
         <v>227</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E40" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -1999,8 +2410,11 @@
       <c r="D41" s="1">
         <v>207</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E41" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>84</v>
       </c>
@@ -2013,8 +2427,11 @@
       <c r="D42" s="1">
         <v>601</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E42" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>86</v>
       </c>
@@ -2027,8 +2444,11 @@
       <c r="D43" s="1">
         <v>228</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E43" s="7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>88</v>
       </c>
@@ -2041,8 +2461,11 @@
       <c r="D44" s="1">
         <v>229</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E44" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>90</v>
       </c>
@@ -2055,8 +2478,11 @@
       <c r="D45" s="1">
         <v>209</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E45" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>92</v>
       </c>
@@ -2069,8 +2495,11 @@
       <c r="D46" s="1">
         <v>230</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E46" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>94</v>
       </c>
@@ -2083,8 +2512,11 @@
       <c r="D47" s="1">
         <v>210</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E47" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>96</v>
       </c>
@@ -2097,8 +2529,11 @@
       <c r="D48" s="1">
         <v>211</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E48" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>98</v>
       </c>
@@ -2111,8 +2546,11 @@
       <c r="D49" s="1">
         <v>231</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E49" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>100</v>
       </c>
@@ -2125,8 +2563,11 @@
       <c r="D50" s="1">
         <v>232</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E50" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>102</v>
       </c>
@@ -2139,8 +2580,11 @@
       <c r="D51" s="1">
         <v>233</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E51" s="7" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>104</v>
       </c>
@@ -2153,8 +2597,11 @@
       <c r="D52" s="1">
         <v>212</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E52" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>106</v>
       </c>
@@ -2167,8 +2614,11 @@
       <c r="D53" s="1">
         <v>214</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E53" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>108</v>
       </c>
@@ -2181,8 +2631,11 @@
       <c r="D54" s="1">
         <v>234</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E54" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>110</v>
       </c>
@@ -2195,8 +2648,11 @@
       <c r="D55" s="1">
         <v>215</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E55" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
         <v>112</v>
       </c>
@@ -2209,8 +2665,11 @@
       <c r="D56" s="1">
         <v>155</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E56" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
         <v>115</v>
       </c>
@@ -2223,8 +2682,11 @@
       <c r="D57" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E57" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
         <v>117</v>
       </c>
@@ -2237,8 +2699,11 @@
       <c r="D58" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E58" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
         <v>119</v>
       </c>
@@ -2251,8 +2716,11 @@
       <c r="D59" s="1">
         <v>156</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E59" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
         <v>121</v>
       </c>
@@ -2265,8 +2733,11 @@
       <c r="D60" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E60" s="7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
         <v>123</v>
       </c>
@@ -2279,8 +2750,11 @@
       <c r="D61" s="1">
         <v>157</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E61" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
         <v>125</v>
       </c>
@@ -2293,8 +2767,11 @@
       <c r="D62" s="1">
         <v>158</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E62" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
         <v>127</v>
       </c>
@@ -2307,8 +2784,11 @@
       <c r="D63" s="1">
         <v>159</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E63" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
         <v>129</v>
       </c>
@@ -2321,8 +2801,11 @@
       <c r="D64" s="1">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E64" s="7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
         <v>131</v>
       </c>
@@ -2335,8 +2818,11 @@
       <c r="D65" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E65" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
         <v>133</v>
       </c>
@@ -2349,8 +2835,11 @@
       <c r="D66" s="1">
         <v>161</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E66" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
         <v>135</v>
       </c>
@@ -2363,8 +2852,11 @@
       <c r="D67" s="1">
         <v>47</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E67" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
         <v>137</v>
       </c>
@@ -2377,8 +2869,11 @@
       <c r="D68" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E68" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
         <v>139</v>
       </c>
@@ -2391,8 +2886,11 @@
       <c r="D69" s="1">
         <v>162</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E69" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
         <v>141</v>
       </c>
@@ -2405,8 +2903,11 @@
       <c r="D70" s="1">
         <v>49</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E70" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
         <v>143</v>
       </c>
@@ -2419,8 +2920,11 @@
       <c r="D71" s="1">
         <v>163</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E71" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
         <v>145</v>
       </c>
@@ -2433,8 +2937,11 @@
       <c r="D72" s="1">
         <v>164</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E72" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
         <v>147</v>
       </c>
@@ -2447,8 +2954,11 @@
       <c r="D73" s="1">
         <v>165</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E73" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
         <v>149</v>
       </c>
@@ -2461,8 +2971,11 @@
       <c r="D74" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E74" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
         <v>151</v>
       </c>
@@ -2475,8 +2988,11 @@
       <c r="D75" s="1">
         <v>166</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E75" s="7" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
         <v>153</v>
       </c>
@@ -2489,8 +3005,11 @@
       <c r="D76" s="1">
         <v>167</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E76" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
         <v>155</v>
       </c>
@@ -2503,8 +3022,11 @@
       <c r="D77" s="1">
         <v>168</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E77" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
         <v>157</v>
       </c>
@@ -2517,8 +3039,11 @@
       <c r="D78" s="1">
         <v>51</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E78" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
         <v>159</v>
       </c>
@@ -2531,8 +3056,11 @@
       <c r="D79" s="1">
         <v>169</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E79" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
         <v>161</v>
       </c>
@@ -2545,8 +3073,11 @@
       <c r="D80" s="1">
         <v>170</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E80" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
         <v>162</v>
       </c>
@@ -2559,8 +3090,11 @@
       <c r="D81" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E81" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
         <v>164</v>
       </c>
@@ -2573,8 +3107,11 @@
       <c r="D82" s="1">
         <v>94</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E82" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
         <v>167</v>
       </c>
@@ -2587,8 +3124,11 @@
       <c r="D83" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E83" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
         <v>169</v>
       </c>
@@ -2601,8 +3141,11 @@
       <c r="D84" s="1">
         <v>96</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E84" s="7" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
         <v>171</v>
       </c>
@@ -2615,8 +3158,11 @@
       <c r="D85" s="1">
         <v>98</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E85" s="7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
         <v>173</v>
       </c>
@@ -2629,8 +3175,11 @@
       <c r="D86" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E86" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
         <v>175</v>
       </c>
@@ -2643,8 +3192,11 @@
       <c r="D87" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E87" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
         <v>177</v>
       </c>
@@ -2657,8 +3209,11 @@
       <c r="D88" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E88" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
         <v>179</v>
       </c>
@@ -2671,8 +3226,11 @@
       <c r="D89" s="1">
         <v>104</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E89" s="7" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
         <v>181</v>
       </c>
@@ -2685,8 +3243,11 @@
       <c r="D90" s="1">
         <v>106</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E90" s="7" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
         <v>183</v>
       </c>
@@ -2699,8 +3260,11 @@
       <c r="D91" s="1">
         <v>107</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E91" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
         <v>185</v>
       </c>
@@ -2713,8 +3277,11 @@
       <c r="D92" s="1">
         <v>131</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E92" s="7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
         <v>187</v>
       </c>
@@ -2727,8 +3294,11 @@
       <c r="D93" s="1">
         <v>130</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E93" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
         <v>189</v>
       </c>
@@ -2741,8 +3311,11 @@
       <c r="D94" s="1">
         <v>132</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E94" s="7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
         <v>191</v>
       </c>
@@ -2755,8 +3328,11 @@
       <c r="D95" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E95" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
         <v>193</v>
       </c>
@@ -2769,8 +3345,11 @@
       <c r="D96" s="1">
         <v>134</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E96" s="7" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
         <v>195</v>
       </c>
@@ -2783,8 +3362,11 @@
       <c r="D97" s="1">
         <v>135</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E97" s="7" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
         <v>197</v>
       </c>
@@ -2797,8 +3379,11 @@
       <c r="D98" s="1">
         <v>136</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E98" s="7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
         <v>199</v>
       </c>
@@ -2811,8 +3396,11 @@
       <c r="D99" s="1">
         <v>137</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E99" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
         <v>201</v>
       </c>
@@ -2825,8 +3413,11 @@
       <c r="D100" s="1">
         <v>138</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E100" s="7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
         <v>203</v>
       </c>
@@ -2839,8 +3430,11 @@
       <c r="D101" s="1">
         <v>139</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E101" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
         <v>205</v>
       </c>
@@ -2853,8 +3447,11 @@
       <c r="D102" s="1">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E102" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
         <v>207</v>
       </c>
@@ -2867,8 +3464,11 @@
       <c r="D103" s="1">
         <v>141</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E103" s="7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
         <v>209</v>
       </c>
@@ -2881,8 +3481,11 @@
       <c r="D104" s="1">
         <v>142</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E104" s="7" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
         <v>211</v>
       </c>
@@ -2895,8 +3498,11 @@
       <c r="D105" s="1">
         <v>144</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E105" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
         <v>213</v>
       </c>
@@ -2909,8 +3515,11 @@
       <c r="D106" s="1">
         <v>145</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E106" s="7" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
         <v>215</v>
       </c>
@@ -2923,8 +3532,11 @@
       <c r="D107" s="1">
         <v>146</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E107" s="7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
         <v>217</v>
       </c>
@@ -2937,8 +3549,11 @@
       <c r="D108" s="1">
         <v>216</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E108" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
         <v>218</v>
       </c>
@@ -2951,8 +3566,11 @@
       <c r="D109" s="1">
         <v>217</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E109" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
         <v>219</v>
       </c>
@@ -2965,8 +3583,11 @@
       <c r="D110" s="1">
         <v>236</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E110" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
         <v>220</v>
       </c>
@@ -2979,8 +3600,11 @@
       <c r="D111" s="1">
         <v>218</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E111" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
         <v>221</v>
       </c>
@@ -2993,8 +3617,11 @@
       <c r="D112" s="1">
         <v>237</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E112" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
         <v>222</v>
       </c>
@@ -3007,8 +3634,11 @@
       <c r="D113" s="1">
         <v>219</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E113" s="7" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
         <v>223</v>
       </c>
@@ -3021,8 +3651,11 @@
       <c r="D114" s="1">
         <v>220</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E114" s="7" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
         <v>224</v>
       </c>
@@ -3035,8 +3668,11 @@
       <c r="D115" s="1">
         <v>235</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E115" s="7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
         <v>225</v>
       </c>
@@ -3049,8 +3685,11 @@
       <c r="D116" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E116" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
         <v>227</v>
       </c>
@@ -3063,8 +3702,11 @@
       <c r="D117" s="1">
         <v>46</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E117" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
         <v>228</v>
       </c>
@@ -3077,8 +3719,11 @@
       <c r="D118" s="1">
         <v>53</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E118" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
         <v>230</v>
       </c>
@@ -3091,8 +3736,11 @@
       <c r="D119" s="1">
         <v>54</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E119" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
         <v>232</v>
       </c>
@@ -3105,8 +3753,11 @@
       <c r="D120" s="1">
         <v>55</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E120" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
         <v>233</v>
       </c>
@@ -3119,8 +3770,11 @@
       <c r="D121" s="1">
         <v>103</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E121" s="7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
         <v>234</v>
       </c>
@@ -3133,8 +3787,11 @@
       <c r="D122" s="1">
         <v>86</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E122" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
         <v>235</v>
       </c>
@@ -3147,8 +3804,11 @@
       <c r="D123" s="1">
         <v>57</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E123" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
         <v>236</v>
       </c>
@@ -3161,8 +3821,11 @@
       <c r="D124" s="1">
         <v>58</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E124" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
         <v>237</v>
       </c>
@@ -3175,8 +3838,11 @@
       <c r="D125" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E125" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
         <v>238</v>
       </c>
@@ -3189,8 +3855,11 @@
       <c r="D126" s="1">
         <v>171</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E126" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
         <v>239</v>
       </c>
@@ -3203,8 +3872,11 @@
       <c r="D127" s="1">
         <v>87</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E127" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
         <v>240</v>
       </c>
@@ -3217,8 +3889,11 @@
       <c r="D128" s="1">
         <v>172</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E128" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
         <v>241</v>
       </c>
@@ -3231,8 +3906,11 @@
       <c r="D129" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E129" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
         <v>242</v>
       </c>
@@ -3245,8 +3923,11 @@
       <c r="D130" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E130" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>243</v>
       </c>
@@ -3259,8 +3940,11 @@
       <c r="D131" s="1">
         <v>89</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E131" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>244</v>
       </c>
@@ -3273,8 +3957,11 @@
       <c r="D132" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E132" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
         <v>245</v>
       </c>
@@ -3287,8 +3974,11 @@
       <c r="D133" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E133" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
         <v>246</v>
       </c>
@@ -3301,8 +3991,11 @@
       <c r="D134" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E134" s="7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
         <v>247</v>
       </c>
@@ -3315,8 +4008,11 @@
       <c r="D135" s="1">
         <v>151</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E135" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
         <v>248</v>
       </c>
@@ -3329,8 +4025,11 @@
       <c r="D136" s="1">
         <v>152</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E136" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
         <v>249</v>
       </c>
@@ -3343,8 +4042,11 @@
       <c r="D137" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E137" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
         <v>250</v>
       </c>
@@ -3357,8 +4059,11 @@
       <c r="D138" s="1">
         <v>153</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E138" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
         <v>251</v>
       </c>
@@ -3371,8 +4076,11 @@
       <c r="D139" s="1">
         <v>121</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E139" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
         <v>252</v>
       </c>
@@ -3385,8 +4093,11 @@
       <c r="D140" s="1">
         <v>93</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E140" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
         <v>253</v>
       </c>
@@ -3399,8 +4110,11 @@
       <c r="D141" s="1">
         <v>154</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E141" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
         <v>257</v>
       </c>
@@ -3413,8 +4127,11 @@
       <c r="D142" s="1">
         <v>97</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E142" s="7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
         <v>259</v>
       </c>
@@ -3427,8 +4144,11 @@
       <c r="D143" s="1">
         <v>102</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E143" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
         <v>261</v>
       </c>
@@ -3440,6 +4160,9 @@
       </c>
       <c r="D144" s="1">
         <v>103</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.15">
@@ -3455,6 +4178,9 @@
       <c r="D145" s="1">
         <v>105</v>
       </c>
+      <c r="E145" s="7" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
@@ -3469,6 +4195,9 @@
       <c r="D146" s="1">
         <v>125</v>
       </c>
+      <c r="E146" s="7" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
@@ -3483,6 +4212,9 @@
       <c r="D147" s="1">
         <v>148</v>
       </c>
+      <c r="E147" s="7" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
@@ -3497,6 +4229,9 @@
       <c r="D148" s="1">
         <v>149</v>
       </c>
+      <c r="E148" s="7" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
@@ -3510,6 +4245,9 @@
       </c>
       <c r="D149" s="1">
         <v>173</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="14.25" x14ac:dyDescent="0.15">
@@ -3557,6 +4295,129 @@
     <hyperlink ref="E25" r:id="rId24" xr:uid="{95F586DA-97A7-1B4E-8CC6-C0D33B0FB054}"/>
     <hyperlink ref="E26" r:id="rId25" xr:uid="{08C8D0D0-F61E-2641-A4C3-D928A3793B65}"/>
     <hyperlink ref="E150" r:id="rId26" xr:uid="{804CCF4C-5A7B-9B48-98CA-E205F3A96300}"/>
+    <hyperlink ref="E28" r:id="rId27" xr:uid="{B028CEB6-DD08-8749-926A-E563F656BC89}"/>
+    <hyperlink ref="E30" r:id="rId28" xr:uid="{B3AB9535-6416-6C4B-9ED7-693D446E30ED}"/>
+    <hyperlink ref="E31" r:id="rId29" xr:uid="{C25D62C1-491E-9F44-AEF6-84F9168DDC7D}"/>
+    <hyperlink ref="E32" r:id="rId30" xr:uid="{09BBA3BB-CC53-6045-9C84-FA6E4CB5A679}"/>
+    <hyperlink ref="E33" r:id="rId31" xr:uid="{4B5C23D8-4A67-D642-B25C-A474CDCF9061}"/>
+    <hyperlink ref="E35" r:id="rId32" xr:uid="{C08438AA-8F17-A748-82A2-36B4B867DD47}"/>
+    <hyperlink ref="E39" r:id="rId33" xr:uid="{732D2120-1E12-B643-945B-2DDE167EDA9A}"/>
+    <hyperlink ref="E41" r:id="rId34" xr:uid="{ED7782D3-E7C0-D646-A518-70730C1F6F4A}"/>
+    <hyperlink ref="E42" r:id="rId35" xr:uid="{C2020A4F-B143-EB43-A6F2-676CAE28616F}"/>
+    <hyperlink ref="E45" r:id="rId36" xr:uid="{7429BCC2-A906-B143-B063-80622B34C6C8}"/>
+    <hyperlink ref="E47" r:id="rId37" xr:uid="{6216D92F-C1B2-3044-A090-ED5BA88988F2}"/>
+    <hyperlink ref="E48" r:id="rId38" xr:uid="{39EFB9FD-FAB2-4C4B-93AF-2E126A48C197}"/>
+    <hyperlink ref="E52" r:id="rId39" xr:uid="{255EAEFD-5973-7F46-B8F2-7B59260A48C2}"/>
+    <hyperlink ref="E53" r:id="rId40" xr:uid="{711813E8-792F-F342-9523-B13160406EC2}"/>
+    <hyperlink ref="E55" r:id="rId41" xr:uid="{5E8FE998-2481-F647-B452-D3D6AED08168}"/>
+    <hyperlink ref="E108" r:id="rId42" xr:uid="{DA546FC0-8830-1549-8665-8240EE6F1046}"/>
+    <hyperlink ref="E109" r:id="rId43" xr:uid="{9AB62CEA-54EF-AC4A-B69E-C81F36B6BE11}"/>
+    <hyperlink ref="E111" r:id="rId44" xr:uid="{E8F445FF-1B87-EA42-80EE-BBD4572B1398}"/>
+    <hyperlink ref="E113" r:id="rId45" xr:uid="{DAB8D699-6786-2E40-8005-630683FE7468}"/>
+    <hyperlink ref="E114" r:id="rId46" xr:uid="{23FF37CB-1412-BF4E-B272-D62A3F64A73B}"/>
+    <hyperlink ref="E27" r:id="rId47" xr:uid="{C381FB86-409A-5A48-808C-9915A05426B3}"/>
+    <hyperlink ref="E29" r:id="rId48" xr:uid="{E4FF04D4-CE11-7E40-AFB4-937325E75C1F}"/>
+    <hyperlink ref="E34" r:id="rId49" xr:uid="{5FE14337-5B1E-654D-8066-C82338B019AA}"/>
+    <hyperlink ref="E36" r:id="rId50" xr:uid="{1C5109AF-2AE9-0A4C-9D2A-408CBC75FF1F}"/>
+    <hyperlink ref="E37" r:id="rId51" xr:uid="{92CFD17B-424B-B849-AAB2-83D259B7E194}"/>
+    <hyperlink ref="E38" r:id="rId52" xr:uid="{F7B39CCD-C76B-B34C-A4AD-5CD90F79F31D}"/>
+    <hyperlink ref="E40" r:id="rId53" xr:uid="{0B217BAA-A2D0-D845-860E-3C9F85F96CFA}"/>
+    <hyperlink ref="E43" r:id="rId54" xr:uid="{50BB76C9-799E-2945-8020-D2F790E85B44}"/>
+    <hyperlink ref="E44" r:id="rId55" xr:uid="{022913D2-1438-1941-B98A-95397C4D352E}"/>
+    <hyperlink ref="E46" r:id="rId56" xr:uid="{7D8A9675-EFD5-4C48-996C-A948754F964E}"/>
+    <hyperlink ref="E49" r:id="rId57" xr:uid="{9E07C30F-F3BB-384A-8A34-C0AEA796E09A}"/>
+    <hyperlink ref="E50" r:id="rId58" xr:uid="{F82C43CE-3179-3642-B749-D1A406B395AA}"/>
+    <hyperlink ref="E51" r:id="rId59" xr:uid="{252B33CC-1D63-0541-BC64-324B1A34AF53}"/>
+    <hyperlink ref="E54" r:id="rId60" xr:uid="{E919C61F-91B9-1543-BE1D-5883FDFD40B1}"/>
+    <hyperlink ref="E115" r:id="rId61" xr:uid="{75A89CD9-F28F-3448-A5FA-33E13F07216D}"/>
+    <hyperlink ref="E110" r:id="rId62" xr:uid="{911CE312-7FF1-CC4F-A013-425E25809F0C}"/>
+    <hyperlink ref="E112" r:id="rId63" xr:uid="{BFBA09BF-1BC2-4547-9754-8A0BE6E2F887}"/>
+    <hyperlink ref="E116" r:id="rId64" xr:uid="{974932F4-6B16-7443-B9E0-1FC58666A13E}"/>
+    <hyperlink ref="E57" r:id="rId65" xr:uid="{FD22DD1B-5637-7D4F-93CB-B348CD5FC1D0}"/>
+    <hyperlink ref="E58" r:id="rId66" xr:uid="{29270ADD-D12C-914C-8F19-EF2067F5622D}"/>
+    <hyperlink ref="E60" r:id="rId67" xr:uid="{84938667-96DC-334A-BB58-233836B58D8E}"/>
+    <hyperlink ref="E117" r:id="rId68" xr:uid="{4717C641-B586-7A43-AE0F-E4682C9DF3C5}"/>
+    <hyperlink ref="E64" r:id="rId69" xr:uid="{B6868123-8E9E-2D40-8362-221382976E30}"/>
+    <hyperlink ref="E67" r:id="rId70" xr:uid="{A6CDB421-AD6B-8D4D-B5F6-67917591A16F}"/>
+    <hyperlink ref="E68" r:id="rId71" xr:uid="{4C1438F1-72F1-B24E-B22B-09707491B27F}"/>
+    <hyperlink ref="E70" r:id="rId72" xr:uid="{22748473-5EC8-C944-A181-CEDACE068082}"/>
+    <hyperlink ref="E74" r:id="rId73" xr:uid="{EF5E47F1-A4E3-0545-B8FF-5D64C3F89207}"/>
+    <hyperlink ref="E78" r:id="rId74" xr:uid="{224BDA5C-5B4E-B44A-8F84-8C1A652A4AD6}"/>
+    <hyperlink ref="E118" r:id="rId75" xr:uid="{1C16FE09-1DCE-9343-99AA-42656F2D62B6}"/>
+    <hyperlink ref="E119" r:id="rId76" xr:uid="{C75C5D3E-3A37-DD4F-8761-CF1E67862B2A}"/>
+    <hyperlink ref="E120" r:id="rId77" xr:uid="{5C41EE6A-3892-794F-813D-F5E5AD195D01}"/>
+    <hyperlink ref="E121" r:id="rId78" xr:uid="{8D004488-79EA-AB4A-9CB0-E5BEBFF7B8FD}"/>
+    <hyperlink ref="E123" r:id="rId79" xr:uid="{537D06E8-171F-834A-B5A4-B7DBEAF458BA}"/>
+    <hyperlink ref="E124" r:id="rId80" xr:uid="{28B3EA17-A533-DD4E-92E5-9E5D52770549}"/>
+    <hyperlink ref="E125" r:id="rId81" xr:uid="{A10C6604-DC93-D846-9F28-AA7253754043}"/>
+    <hyperlink ref="E126" r:id="rId82" xr:uid="{4697061B-3362-114A-92D3-2EF937FCF871}"/>
+    <hyperlink ref="E128" r:id="rId83" xr:uid="{6CC38C36-4C39-CE49-8764-494EA716F5BD}"/>
+    <hyperlink ref="E130" r:id="rId84" xr:uid="{4BB46285-6920-684E-84D7-5D73F6C2AB2E}"/>
+    <hyperlink ref="E132" r:id="rId85" xr:uid="{A55E8962-6237-984E-B17E-39AF9D579157}"/>
+    <hyperlink ref="E135" r:id="rId86" xr:uid="{A9B4CCE6-3D05-DE46-9305-FC2C6527E9E8}"/>
+    <hyperlink ref="E136" r:id="rId87" xr:uid="{809958CE-04A5-7C48-AE37-83740956ED1A}"/>
+    <hyperlink ref="E138" r:id="rId88" xr:uid="{AEE48B7B-5C82-A64C-A0EC-0FA7A968BA82}"/>
+    <hyperlink ref="E139" r:id="rId89" xr:uid="{81FF53A1-1636-7F40-8FB8-395E4AFBE343}"/>
+    <hyperlink ref="E141" r:id="rId90" xr:uid="{4CC08314-D733-5D41-AEF6-5158A03288BA}"/>
+    <hyperlink ref="E56" r:id="rId91" xr:uid="{193E40BB-8A11-284C-8E21-C16498593A47}"/>
+    <hyperlink ref="E59" r:id="rId92" xr:uid="{6BCF8BEA-A7E4-BC4E-A73C-242DAB732AF0}"/>
+    <hyperlink ref="E61" r:id="rId93" xr:uid="{2683B2A1-7102-724E-A41A-CCB3C7A551D3}"/>
+    <hyperlink ref="E62" r:id="rId94" xr:uid="{3DF70F58-4369-FA47-959A-18BC94E7B982}"/>
+    <hyperlink ref="E63" r:id="rId95" xr:uid="{08BD8F57-2160-DD45-855C-BE2A9F534CB0}"/>
+    <hyperlink ref="E65" r:id="rId96" xr:uid="{4C3F92A9-DC0F-FF4A-93C8-C58A39833106}"/>
+    <hyperlink ref="E66" r:id="rId97" xr:uid="{E7A77406-02A6-FF49-A994-C1376C734C5F}"/>
+    <hyperlink ref="E69" r:id="rId98" xr:uid="{A3B22346-A5F0-6547-A0D7-8201CFCBCAE1}"/>
+    <hyperlink ref="E71" r:id="rId99" xr:uid="{4DBF216B-6E04-8E43-B9C4-A4FBE7FD6195}"/>
+    <hyperlink ref="E72" r:id="rId100" xr:uid="{268B130D-95CE-624F-84AE-D1006D9AFABB}"/>
+    <hyperlink ref="E73" r:id="rId101" xr:uid="{71593EF7-2C62-F141-9499-43064751168A}"/>
+    <hyperlink ref="E75" r:id="rId102" xr:uid="{68121539-85A5-D24D-90ED-13CEFCAD62DE}"/>
+    <hyperlink ref="E76" r:id="rId103" xr:uid="{FDF75A87-DF69-3A41-9A7D-65F87B1F4BF4}"/>
+    <hyperlink ref="E77" r:id="rId104" xr:uid="{BF6FF12D-FAE1-F942-898F-F21DAF3F5C7B}"/>
+    <hyperlink ref="E79" r:id="rId105" xr:uid="{FBE4336B-7ECD-4241-B663-D67F0DF0819F}"/>
+    <hyperlink ref="E80" r:id="rId106" xr:uid="{FB3C2E7D-5141-164C-B8AD-75A3652BDB8E}"/>
+    <hyperlink ref="E81" r:id="rId107" xr:uid="{A8E500DF-983B-EB45-9C7D-D7AAAA2EF7E3}"/>
+    <hyperlink ref="E122" r:id="rId108" xr:uid="{A3438A6C-6A75-734E-9E36-4EE7D3F4508A}"/>
+    <hyperlink ref="E127" r:id="rId109" xr:uid="{508797AD-E206-894D-ADA4-CC15D90BB3B2}"/>
+    <hyperlink ref="E129" r:id="rId110" xr:uid="{FA72B67B-F3A9-5942-8AE6-B0D5EFB886A8}"/>
+    <hyperlink ref="E131" r:id="rId111" xr:uid="{6DD9592A-3A3D-6E45-B2E3-9E97EF54F07E}"/>
+    <hyperlink ref="E133" r:id="rId112" xr:uid="{8DD92156-4AC8-8543-8541-B327D0EAA86E}"/>
+    <hyperlink ref="E134" r:id="rId113" xr:uid="{2B98D22C-B5CB-454D-B700-F57689213869}"/>
+    <hyperlink ref="E137" r:id="rId114" xr:uid="{A160B441-8CBB-F147-912B-5A2B4EF0311F}"/>
+    <hyperlink ref="E140" r:id="rId115" xr:uid="{47D30BDD-8F4B-C94E-89A1-E74EFBA30BA9}"/>
+    <hyperlink ref="E82" r:id="rId116" xr:uid="{19CE38DE-28B4-0048-B5C7-F4A107C324BE}"/>
+    <hyperlink ref="E83" r:id="rId117" xr:uid="{AC19CC9E-B955-5347-AB35-16E7B39524FE}"/>
+    <hyperlink ref="E84" r:id="rId118" xr:uid="{1D13D381-B9F9-7440-AE7C-50CBA06C0754}"/>
+    <hyperlink ref="E142" r:id="rId119" xr:uid="{3F495FDB-937A-2E4A-976A-F4C6C0287700}"/>
+    <hyperlink ref="E85" r:id="rId120" xr:uid="{17FFA948-709B-E94B-A3DF-F7B752D55478}"/>
+    <hyperlink ref="E86" r:id="rId121" xr:uid="{256E8767-3C0E-6646-A79A-12468E427552}"/>
+    <hyperlink ref="E87" r:id="rId122" xr:uid="{AF6E1C9B-F245-1A42-A19F-7DA19ED0BB2F}"/>
+    <hyperlink ref="E88" r:id="rId123" xr:uid="{78F275FA-65BE-6045-B995-05991FA41A8C}"/>
+    <hyperlink ref="E143" r:id="rId124" xr:uid="{DE1FB4F4-C835-7940-BA22-B17D06D71366}"/>
+    <hyperlink ref="E144" r:id="rId125" xr:uid="{DB407FDE-3930-6346-91EE-45DEECBAACEB}"/>
+    <hyperlink ref="E89" r:id="rId126" xr:uid="{8425D5DA-AE59-AF4F-BF21-707BDE1A496A}"/>
+    <hyperlink ref="E145" r:id="rId127" xr:uid="{980B9185-00D9-FF4B-ADCD-E239328A576D}"/>
+    <hyperlink ref="E90" r:id="rId128" xr:uid="{C69F6C2F-D84D-1548-8D70-5CB75D2AA242}"/>
+    <hyperlink ref="E91" r:id="rId129" xr:uid="{E8C59134-9A0A-7149-8394-B405C29E2D43}"/>
+    <hyperlink ref="E93" r:id="rId130" xr:uid="{7AC1B5CE-BE82-4C44-B6B6-D0B901773138}"/>
+    <hyperlink ref="E92" r:id="rId131" xr:uid="{312A32BD-5F53-554D-B2F6-D68D52954818}"/>
+    <hyperlink ref="E94" r:id="rId132" xr:uid="{C9BD46D3-F614-AF41-96EF-0875DF94F141}"/>
+    <hyperlink ref="E95" r:id="rId133" xr:uid="{B90D00BD-DA37-2645-9312-9B50BE6ECC7E}"/>
+    <hyperlink ref="E96" r:id="rId134" xr:uid="{F4F0BCA8-4818-6E41-A5D3-28482206DD3E}"/>
+    <hyperlink ref="E97" r:id="rId135" xr:uid="{81B494A9-25D6-7741-8E40-A347A2F8D4A8}"/>
+    <hyperlink ref="E98" r:id="rId136" xr:uid="{612B5673-760D-9941-B1C4-B1F8E4E7019D}"/>
+    <hyperlink ref="E99" r:id="rId137" xr:uid="{1FAA2CA2-353A-A546-A851-D203B7568B70}"/>
+    <hyperlink ref="E100" r:id="rId138" xr:uid="{129EA43C-41D6-A441-9210-66887CB62A69}"/>
+    <hyperlink ref="E101" r:id="rId139" xr:uid="{21B8CF7B-F762-BE49-8526-36342F761253}"/>
+    <hyperlink ref="E102" r:id="rId140" xr:uid="{EC656FC4-12E8-3046-BB12-2BD25E78D141}"/>
+    <hyperlink ref="E103" r:id="rId141" xr:uid="{A32237AC-2927-704F-A78B-8239EAF0DF0D}"/>
+    <hyperlink ref="E104" r:id="rId142" xr:uid="{6FA18071-934A-0346-8AE3-4E5141BEAD54}"/>
+    <hyperlink ref="E105" r:id="rId143" xr:uid="{AA6ED195-F3B0-7D4C-9139-9052660161D5}"/>
+    <hyperlink ref="E106" r:id="rId144" xr:uid="{09DDCF7A-143D-FB45-BA69-53DE86A300AC}"/>
+    <hyperlink ref="E107" r:id="rId145" xr:uid="{6E522034-7E97-494E-B6FD-95754118B3FC}"/>
+    <hyperlink ref="E146" r:id="rId146" xr:uid="{291FFE27-6369-E64B-B734-C4D9932BA4C1}"/>
+    <hyperlink ref="E147" r:id="rId147" xr:uid="{A5715137-7017-A242-B24F-5031A20A87E9}"/>
+    <hyperlink ref="E148" r:id="rId148" xr:uid="{14D16191-60F8-2748-AB4A-D12D88490382}"/>
+    <hyperlink ref="E149" r:id="rId149" xr:uid="{CE57A227-A2BE-F143-AB31-2C534C26A3D3}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
